--- a/output/pdf_financials_xlsx/DEF.xlsx
+++ b/output/pdf_financials_xlsx/DEF.xlsx
@@ -4302,25 +4302,25 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.277202</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.830111</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.013494</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.80535</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.335982</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>6.17634</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>6.79057</v>
       </c>
     </row>
     <row r="93">
@@ -5357,25 +5357,25 @@
         <v>0</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.010733</v>
+        <v>-1.644188</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-1.500917</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-1.628071</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-4.711268</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-6.393064</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-6.563498</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0.262489</v>
+        <v>-5.121638</v>
       </c>
     </row>
     <row r="119">
@@ -7267,7 +7267,11 @@
           <t>Share-based payment reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -8160,7 +8164,11 @@
           <t>Share-based payment reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -10932,7 +10940,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DEF.xlsx
+++ b/output/pdf_financials_xlsx/DEF.xlsx
@@ -809,25 +809,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.028645</v>
+        <v>0.83465</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.411653</v>
+        <v>0.99752</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.132879</v>
+        <v>1.120455</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.021265</v>
+        <v>2.959307</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.160068</v>
+        <v>4.017649</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.758491</v>
+        <v>3.245019</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.234869</v>
+        <v>2.114711</v>
       </c>
     </row>
     <row r="11">
@@ -853,25 +853,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.028645</v>
+        <v>-0.83465</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.411653</v>
+        <v>-0.99752</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.132879</v>
+        <v>-1.120455</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.021265</v>
+        <v>-2.959307</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.160068</v>
+        <v>-4.017649</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.758491</v>
+        <v>-3.245019</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.234869</v>
+        <v>-2.114711</v>
       </c>
     </row>
     <row r="12">
@@ -886,10 +886,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002506</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.002781</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -897,25 +897,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000951</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>2.5e-05</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.027403</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.070239</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.21333</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.084649</v>
       </c>
     </row>
     <row r="13">
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.201817</v>
+        <v>-0.204323</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.317042</v>
+        <v>-0.319823</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1601,25 +1601,25 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.863295</v>
+        <v>-0.864246</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.409173</v>
+        <v>-1.409401</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.253334</v>
+        <v>-1.253359</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.938042</v>
+        <v>-2.965445</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.857581</v>
+        <v>-3.92782</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.486528</v>
+        <v>-2.699858</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.34958</v>
+        <v>-2.434229</v>
       </c>
     </row>
     <row r="28">
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.201817</v>
+        <v>-0.204323</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.317042</v>
+        <v>-0.319823</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1689,25 +1689,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.863295</v>
+        <v>-0.864246</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.409173</v>
+        <v>-1.409401</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.253334</v>
+        <v>-1.253359</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.938042</v>
+        <v>-2.965445</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.857581</v>
+        <v>-3.92782</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.486528</v>
+        <v>-2.699858</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.34958</v>
+        <v>-2.434229</v>
       </c>
     </row>
     <row r="30">
@@ -1901,19 +1901,19 @@
         <v>0.455776</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.339848</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.118621</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.129811</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.569031</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>20.831725</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>11.783088</v>
@@ -1981,19 +1981,19 @@
         <v>0.455776</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.339848</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.118621</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.129811</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.569031</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>20.831725</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>11.783088</v>
@@ -2461,19 +2461,19 @@
         <v>0.01521</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.341991</v>
+        <v>0.002143</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.119663</v>
+        <v>0.001042</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.261471</v>
+        <v>0.13166</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.61316</v>
+        <v>0.044129</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>21.486716</v>
+        <v>0.654991</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.55344</v>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -21368,7 +21368,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -21392,25 +21392,25 @@
         </is>
       </c>
       <c r="I219" s="5" t="n">
-        <v>-0.83465</v>
+        <v>0.83465</v>
       </c>
       <c r="J219" s="5" t="n">
-        <v>-0.99752</v>
+        <v>0.99752</v>
       </c>
       <c r="K219" s="5" t="n">
-        <v>-1.120455</v>
+        <v>1.120455</v>
       </c>
       <c r="L219" s="5" t="n">
-        <v>-2.959307</v>
+        <v>2.959307</v>
       </c>
       <c r="M219" s="5" t="n">
-        <v>-4.017649</v>
+        <v>4.017649</v>
       </c>
       <c r="N219" s="5" t="n">
-        <v>-3.245019</v>
+        <v>3.245019</v>
       </c>
       <c r="O219" s="5" t="n">
-        <v>-2.114711</v>
+        <v>2.114711</v>
       </c>
     </row>
     <row r="220">
@@ -21431,7 +21431,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -22444,7 +22444,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -23294,7 +23294,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">

--- a/output/pdf_financials_xlsx/DEF.xlsx
+++ b/output/pdf_financials_xlsx/DEF.xlsx
@@ -528,10 +528,8 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -572,10 +570,8 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -583,10 +579,8 @@
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -616,10 +610,8 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -660,10 +652,8 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.019384</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.066736</v>
@@ -671,10 +661,8 @@
       <c r="D7" s="3" t="n">
         <v>0.117486</v>
       </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0.492271</v>
@@ -704,10 +692,8 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
@@ -715,10 +701,8 @@
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -748,10 +732,8 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0</v>
@@ -759,10 +741,8 @@
       <c r="D9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -792,10 +772,8 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.019384</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.066736</v>
@@ -803,10 +781,8 @@
       <c r="D10" s="3" t="n">
         <v>0.117486</v>
       </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0.83465</v>
@@ -836,10 +812,8 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.019384</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.204323</v>
@@ -880,10 +854,8 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0.002506</v>
@@ -891,10 +863,8 @@
       <c r="D12" s="3" t="n">
         <v>0.002781</v>
       </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0.000951</v>
@@ -924,10 +894,8 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>-0</v>
@@ -935,10 +903,8 @@
       <c r="D13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>-0</v>
@@ -968,10 +934,8 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>0</v>
@@ -979,10 +943,8 @@
       <c r="D14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>0</v>
@@ -1012,10 +974,8 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0</v>
@@ -1023,10 +983,8 @@
       <c r="D15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>-0.029596</v>
@@ -1056,21 +1014,17 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.039586</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.201817</v>
+        <v>-0.317042</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.317042</v>
       </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E16" s="3" t="n">
+        <v>-1.22067</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-0.863295</v>
@@ -1100,10 +1054,8 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -1111,10 +1063,8 @@
       <c r="D17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -1268,21 +1218,17 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.039586</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-0.201817</v>
+        <v>-0.317042</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.317042</v>
       </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E20" s="3" t="n">
+        <v>-1.22067</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-0.863295</v>
@@ -1312,10 +1258,8 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -1323,10 +1267,8 @@
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>0</v>
@@ -1356,10 +1298,8 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>0</v>
@@ -1367,10 +1307,8 @@
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>0</v>
@@ -1400,13 +1338,11 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-0.039586</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-0.201817</v>
+        <v>-0.317042</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-0.317042</v>
@@ -1442,10 +1378,8 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>0.02</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>-0.03</v>
@@ -1486,10 +1420,8 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>0.02</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>-0.03</v>
@@ -1530,13 +1462,11 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>-1.9793</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>6.727233</v>
+        <v>10.568067</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>7.92605</v>
@@ -1584,21 +1514,17 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.039586</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.204323</v>
+        <v>-0.319548</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.319823</v>
       </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E27" s="3" t="n">
+        <v>-1.22067</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.864246</v>
@@ -1628,10 +1554,8 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0</v>
@@ -1639,10 +1563,8 @@
       <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0</v>
@@ -1672,21 +1594,17 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.039586</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.204323</v>
+        <v>-0.319548</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.319823</v>
       </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E29" s="3" t="n">
+        <v>-1.22067</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.864246</v>
@@ -1778,10 +1696,8 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -1789,10 +1705,8 @@
       <c r="D31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -3133,16 +3047,16 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.003074</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.026281</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.108151</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.280409</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0</v>
@@ -3262,25 +3176,25 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.374387</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.515567</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.174767</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.259917</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.098276</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.15412</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -6123,7 +6037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O252"/>
+  <dimension ref="A1:O284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12097,7 +12011,11 @@
           <t>Share issuance – private placement 26,443,500 2,589,650 54,700</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -15130,7 +15048,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -22854,34 +22776,28 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Legal and audit                                                     176,066                            39,360</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Management fee (Note 8)</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Management fees (Note</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F241" s="5" t="n">
-        <v>0.03525</v>
+        <v>0.078137</v>
       </c>
       <c r="G241" s="5" t="n">
-        <v>0.078137</v>
-      </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.290456</v>
+      </c>
+      <c r="H241" s="5" t="n">
+        <v>9e-06</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
@@ -22927,34 +22843,28 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Office and administration                                              47,575                              2,535</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Office and bank charges</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Project evaluation (Note</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F242" s="5" t="n">
-        <v>0.006487</v>
+        <v>0.026064</v>
       </c>
       <c r="G242" s="5" t="n">
-        <v>0.002535</v>
-      </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.003626</v>
+      </c>
+      <c r="H242" s="5" t="n">
+        <v>9e-06</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
@@ -23000,34 +22910,28 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Office and administration                                              47,575                              2,535</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Share-based compensation (Note</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F243" s="5" t="n">
-        <v>0.026083</v>
+        <v>0.136913</v>
       </c>
       <c r="G243" s="5" t="n">
-        <v>0.03936</v>
-      </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0386</v>
+      </c>
+      <c r="H243" s="5" t="n">
+        <v>8e-06</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -23073,12 +22977,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OPERATING LOSS                                                      (746,361)                            (319,823)</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Project evaluation (Note 8)</t>
+          <t>Write-off of mineral property interest (Note</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -23087,16 +22991,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F244" s="5" t="n">
-        <v>0.03937</v>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G244" s="5" t="n">
-        <v>0.026064</v>
-      </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.468942</v>
+      </c>
+      <c r="H244" s="5" t="n">
+        <v>6e-06</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -23142,12 +23046,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares        Capital       Received     Reserves           Deficit             Total</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Stock-based compensation (Note 6)</t>
+          <t>Balance, July 1, 2010 10,676,250 $ 734,146 $ - $</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -23157,15 +23061,13 @@
         </is>
       </c>
       <c r="F245" s="5" t="n">
-        <v>0.072134</v>
+        <v>0.514534</v>
       </c>
       <c r="G245" s="5" t="n">
-        <v>0.136913</v>
-      </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.283549</v>
+      </c>
+      <c r="H245" s="5" t="n">
+        <v>0.06393699999999999</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -23211,29 +23113,27 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares issued for</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Loss before other item</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Private placement 1,875,000 300,000 -</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F246" s="5" t="n">
-        <v>-0.204323</v>
-      </c>
-      <c r="G246" s="5" t="n">
-        <v>-0.319823</v>
+        <v>0.3</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -23284,29 +23184,27 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>OTHER ITEM</t>
+          <t>Shares issued for</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Share issue costs - (4,642) -</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F247" s="5" t="n">
-        <v>0.002506</v>
-      </c>
-      <c r="G247" s="5" t="n">
-        <v>0.002781</v>
+        <v>-0.004642</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -23357,29 +23255,27 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>OTHER ITEM</t>
+          <t>Mineral property</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for year</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Mineral property interests 675,000 168,750 -</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F248" s="5" t="n">
-        <v>-0.201817</v>
-      </c>
-      <c r="G248" s="5" t="n">
-        <v>-0.317042</v>
+        <v>0.16875</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -23430,12 +23326,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>OTHER ITEM</t>
+          <t>Exercise of</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Deficit, beginning of year</t>
+          <t>Exercise of share options 180,000 43,673 -</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -23445,15 +23341,15 @@
         </is>
       </c>
       <c r="F249" s="5" t="n">
-        <v>-0.081732</v>
-      </c>
-      <c r="G249" s="5" t="n">
-        <v>-0.283549</v>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.024</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H249" s="5" t="n">
+        <v>-0.019673</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -23499,12 +23395,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>OTHER ITEM</t>
+          <t>Share-based</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Deficit, end of year $</t>
+          <t>Share-based compensation - - -</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -23514,15 +23410,15 @@
         </is>
       </c>
       <c r="F250" s="5" t="n">
-        <v>-0.283549</v>
-      </c>
-      <c r="G250" s="5" t="n">
-        <v>-0.600591</v>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.136913</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H250" s="5" t="n">
+        <v>0.136913</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -23568,17 +23464,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>OTHER ITEM</t>
+          <t>Share-based</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted $</t>
+          <t>Net loss for the year - - -</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -23587,10 +23483,10 @@
         </is>
       </c>
       <c r="F251" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-0.317042</v>
       </c>
       <c r="G251" s="5" t="n">
-        <v>-4e-08</v>
+        <v>-0.317042</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -23641,66 +23537,2342 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
+          <t>Share-based</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Balance, June 30, 2011 13,406,250 1,241,927 -</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F252" s="5" t="n">
+        <v>0.822513</v>
+      </c>
+      <c r="G252" s="5" t="n">
+        <v>-0.600591</v>
+      </c>
+      <c r="H252" s="5" t="n">
+        <v>0.181177</v>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Mineral property</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Mineral property interests 2,830,500 1,450,665 -</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F253" s="5" t="n">
+        <v>1.450665</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Mineral property</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Private placement 1,144,500 572,250 -</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F254" s="5" t="n">
+        <v>0.57225</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Mineral property</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Share issue costs - (11,177) -</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F255" s="5" t="n">
+        <v>-0.011177</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Share subscriptions</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Share subscriptions received - - 30,000</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F256" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Share subscriptions</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Net loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F257" s="5" t="n">
+        <v>-1.22067</v>
+      </c>
+      <c r="G257" s="5" t="n">
+        <v>-1.22067</v>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Share subscriptions</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Balance, June 30, 2012 17,381,250 $ 3,253,665 $ 30,000 $</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F258" s="5" t="n">
+        <v>-1.682181</v>
+      </c>
+      <c r="G258" s="5" t="n">
+        <v>-1.821261</v>
+      </c>
+      <c r="H258" s="5" t="n">
+        <v>0.219777</v>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Management fee (Note 8)</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F259" s="5" t="n">
+        <v>0.03525</v>
+      </c>
+      <c r="G259" s="5" t="n">
+        <v>0.078137</v>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Office and bank charges</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F260" s="5" t="n">
+        <v>0.006487</v>
+      </c>
+      <c r="G260" s="5" t="n">
+        <v>0.002535</v>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F261" s="5" t="n">
+        <v>0.026083</v>
+      </c>
+      <c r="G261" s="5" t="n">
+        <v>0.03936</v>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Project evaluation (Note 8)</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F262" s="5" t="n">
+        <v>0.03937</v>
+      </c>
+      <c r="G262" s="5" t="n">
+        <v>0.026064</v>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Stock-based compensation (Note 6)</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F263" s="5" t="n">
+        <v>0.072134</v>
+      </c>
+      <c r="G263" s="5" t="n">
+        <v>0.136913</v>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Loss before other item</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F264" s="5" t="n">
+        <v>-0.204323</v>
+      </c>
+      <c r="G264" s="5" t="n">
+        <v>-0.319823</v>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
           <t>OTHER ITEM</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr">
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F265" s="5" t="n">
+        <v>0.002506</v>
+      </c>
+      <c r="G265" s="5" t="n">
+        <v>0.002781</v>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>OTHER ITEM</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for year</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F266" s="5" t="n">
+        <v>-0.201817</v>
+      </c>
+      <c r="G266" s="5" t="n">
+        <v>-0.317042</v>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>OTHER ITEM</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Deficit, beginning of year</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F267" s="5" t="n">
+        <v>-0.081732</v>
+      </c>
+      <c r="G267" s="5" t="n">
+        <v>-0.283549</v>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>OTHER ITEM</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Deficit, end of year $</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F268" s="5" t="n">
+        <v>-0.283549</v>
+      </c>
+      <c r="G268" s="5" t="n">
+        <v>-0.600591</v>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>OTHER ITEM</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Loss per share, basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F269" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="G269" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>OTHER ITEM</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
         <is>
           <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr">
+      <c r="D270" t="inlineStr">
         <is>
           <t>SharesOutstanding</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F252" s="5" t="n">
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F270" s="5" t="n">
         <v>6.43137</v>
       </c>
-      <c r="G252" s="5" t="n">
+      <c r="G270" s="5" t="n">
         <v>7.63339</v>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O252" t="inlineStr">
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Stock-based compensation $</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F271" s="5" t="n">
+        <v>0.072134</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Project evaluation</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" s="5" t="n">
+        <v>0.03937</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Management fee (note 9)</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E273" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" s="5" t="n">
+        <v>0.03525</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Audit</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" s="5" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F274" s="5" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E275" s="5" t="n">
+        <v>0.019259</v>
+      </c>
+      <c r="F275" s="5" t="n">
+        <v>0.019499</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Office and bank charges</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E276" s="5" t="n">
+        <v>0.000125</v>
+      </c>
+      <c r="F276" s="5" t="n">
+        <v>0.006487</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E277" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" s="5" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E278" s="5" t="n">
+        <v>0.017608</v>
+      </c>
+      <c r="F278" s="5" t="n">
+        <v>0.002583</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" s="5" t="n">
+        <v>-0.003406</v>
+      </c>
+      <c r="F279" s="5" t="n">
+        <v>-0.002506</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Net Loss and Comprehensive Loss for Year</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E280" s="5" t="n">
+        <v>-0.039586</v>
+      </c>
+      <c r="F280" s="5" t="n">
+        <v>-0.201817</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Deficit, Beginning of Year</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" s="5" t="n">
+        <v>-0.042146</v>
+      </c>
+      <c r="F281" s="5" t="n">
+        <v>-0.081732</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Deficit, End of Year $</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" s="5" t="n">
+        <v>-0.081732</v>
+      </c>
+      <c r="F282" s="5" t="n">
+        <v>-0.283549</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Loss Per Share, Basic and Diluted $</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E283" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+      <c r="F283" s="5" t="n">
+        <v>3e-08</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Common Shares Outstanding</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E284" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F284" s="5" t="n">
+        <v>6.43137</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
         <is>
           <t>-</t>
         </is>
